--- a/data/trans_dic/IP1009-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1009-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen transtornos intestinales crónicos</t>
+          <t>Menores que padecen transtornos intestinales crónicos (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -797,22 +798,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,03</t>
+          <t>0,1; 1,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,3</t>
+          <t>0,14; 1,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,31</t>
+          <t>0,15; 1,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,9</t>
+          <t>0,19; 0,94</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
     </row>
@@ -1012,17 +1013,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,93</t>
+          <t>0,11; 1,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,86</t>
+          <t>0,09; 0,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1032,22 +1033,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,93</t>
+          <t>0,09; 0,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,49</t>
+          <t>0,08; 0,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,35</t>
+          <t>0,0; 0,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,74</t>
+          <t>0,19; 0,72</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen transtornos intestinales crónicos (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3647</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3330</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2519</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4534</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2259</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3211</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>455; 5528</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>677; 5544</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3096</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>709; 6397</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>697; 6194</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4404</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1847; 9050</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3551</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4503</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3187</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3050</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2585</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3153</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5287</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3703</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5022</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>769; 7162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>677; 5556</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3114</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>674; 6732</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1082; 7295</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5119</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2681; 10498</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1009-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1009-Estudios-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,17</t>
+          <t>0,1; 1,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,16</t>
+          <t>0,14; 1,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,31</t>
+          <t>0,15; 1,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,69</t>
+          <t>0,08; 0,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,94</t>
+          <t>0,2; 0,89</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,02</t>
+          <t>0,09; 0,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,9</t>
+          <t>0,09; 0,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,52</t>
+          <t>0,08; 0,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,35</t>
+          <t>0,04; 0,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,72</t>
+          <t>0,18; 0,72</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3647</t>
+          <t>0; 3346</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3330</t>
+          <t>0; 3325</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2259</t>
+          <t>0; 2245</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3211</t>
+          <t>0; 3563</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>455; 5528</t>
+          <t>457; 5867</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>677; 5544</t>
+          <t>678; 5925</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3096</t>
+          <t>0; 3745</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>709; 6397</t>
+          <t>737; 6808</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>697; 6194</t>
+          <t>688; 6265</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4404</t>
+          <t>0; 4440</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1847; 9050</t>
+          <t>1903; 8514</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3551</t>
+          <t>0; 3803</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4503</t>
+          <t>0; 3826</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3187</t>
+          <t>0; 3443</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3050</t>
+          <t>0; 4297</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3703</t>
+          <t>0; 4250</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5022</t>
+          <t>0; 4580</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>769; 7162</t>
+          <t>606; 6369</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>677; 5556</t>
+          <t>681; 5568</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3114</t>
+          <t>0; 3115</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>674; 6732</t>
+          <t>668; 6869</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1082; 7295</t>
+          <t>1143; 7454</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5119</t>
+          <t>618; 5130</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2681; 10498</t>
+          <t>2566; 10422</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1009-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1009-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,22 +630,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,72%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,37 +788,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,14; 1,3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,76</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,14; 1,31</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,54</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,79</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 1,24</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,14; 1,24</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,39</t>
+          <t>0,1; 1,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,7</t>
+          <t>0,08; 0,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,89</t>
+          <t>0,16; 0,9</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,37 +1008,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,09; 0,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,9</t>
+          <t>0,1; 0,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,77</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,92</t>
+          <t>0,11; 0,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,53</t>
+          <t>0,08; 0,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,72</t>
+          <t>0,17; 0,74</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1205,22 +1205,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>665</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3346</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3354</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3325</t>
+          <t>0; 3363</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>448</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>637</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1832</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2245</t>
+          <t>680; 6200</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3563</t>
+          <t>0; 3732</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>457; 5867</t>
+          <t>667; 6423</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>678; 5925</t>
+          <t>0; 2248</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3745</t>
+          <t>0; 3205</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>737; 6808</t>
+          <t>455; 4887</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>688; 6265</t>
+          <t>691; 6167</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4440</t>
+          <t>0; 4407</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1903; 8514</t>
+          <t>1563; 8685</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>753</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3803</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3826</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2909</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3542</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3443</t>
+          <t>0; 3618</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4297</t>
+          <t>0; 3836</t>
         </is>
       </c>
     </row>
@@ -1689,27 +1689,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1081</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2585</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4250</t>
+          <t>675; 6206</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4580</t>
+          <t>0; 3140</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>606; 6369</t>
+          <t>716; 6921</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>681; 5568</t>
+          <t>0; 3695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3115</t>
+          <t>0; 4504</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>668; 6869</t>
+          <t>754; 6577</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1143; 7454</t>
+          <t>1083; 6856</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>618; 5130</t>
+          <t>618; 5151</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2566; 10422</t>
+          <t>2472; 10690</t>
         </is>
       </c>
     </row>
